--- a/data/predicted/tft_prediction_results.xlsx
+++ b/data/predicted/tft_prediction_results.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,10 +477,15 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>y3_pred</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>y4_pred</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>y5_pred</t>
         </is>
@@ -506,16 +511,19 @@
         <v>23.4</v>
       </c>
       <c r="G2" t="n">
-        <v>50.6873779296875</v>
+        <v>57.57724380493164</v>
       </c>
       <c r="H2" t="n">
-        <v>55.61291885375977</v>
+        <v>49.5848388671875</v>
       </c>
       <c r="I2" t="n">
-        <v>55.47941589355469</v>
+        <v>2181.70947265625</v>
       </c>
       <c r="J2" t="n">
-        <v>22.45817565917969</v>
+        <v>65.66964721679688</v>
+      </c>
+      <c r="K2" t="n">
+        <v>14.16760540008545</v>
       </c>
     </row>
     <row r="3">
@@ -538,16 +546,19 @@
         <v>23.5</v>
       </c>
       <c r="G3" t="n">
-        <v>45.68510818481445</v>
+        <v>52.66412734985352</v>
       </c>
       <c r="H3" t="n">
-        <v>55.96796798706055</v>
+        <v>53.1061897277832</v>
       </c>
       <c r="I3" t="n">
-        <v>49.10073852539062</v>
+        <v>2284.497314453125</v>
       </c>
       <c r="J3" t="n">
-        <v>24.9309139251709</v>
+        <v>55.74831390380859</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.32886505126953</v>
       </c>
     </row>
     <row r="4">
@@ -570,16 +581,19 @@
         <v>22.9</v>
       </c>
       <c r="G4" t="n">
-        <v>41.772705078125</v>
+        <v>51.47104644775391</v>
       </c>
       <c r="H4" t="n">
-        <v>66.49899291992188</v>
+        <v>65.97673034667969</v>
       </c>
       <c r="I4" t="n">
-        <v>36.69314956665039</v>
+        <v>2176.286376953125</v>
       </c>
       <c r="J4" t="n">
-        <v>28.01525115966797</v>
+        <v>57.58232498168945</v>
+      </c>
+      <c r="K4" t="n">
+        <v>21.85567474365234</v>
       </c>
     </row>
     <row r="5">
@@ -602,16 +616,19 @@
         <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>44.16320037841797</v>
+        <v>61.51594543457031</v>
       </c>
       <c r="H5" t="n">
-        <v>60.74430847167969</v>
+        <v>80.52114105224609</v>
       </c>
       <c r="I5" t="n">
-        <v>56.51473236083984</v>
+        <v>1944.905151367188</v>
       </c>
       <c r="J5" t="n">
-        <v>26.65788650512695</v>
+        <v>45.94529342651367</v>
+      </c>
+      <c r="K5" t="n">
+        <v>13.45126056671143</v>
       </c>
     </row>
     <row r="6">
@@ -634,16 +651,19 @@
         <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>44.47652435302734</v>
+        <v>68.52776336669922</v>
       </c>
       <c r="H6" t="n">
-        <v>64.86164093017578</v>
+        <v>70.26535797119141</v>
       </c>
       <c r="I6" t="n">
-        <v>39.83979415893555</v>
+        <v>1319.404418945312</v>
       </c>
       <c r="J6" t="n">
-        <v>26.64734268188477</v>
+        <v>61.53212356567383</v>
+      </c>
+      <c r="K6" t="n">
+        <v>18.8213005065918</v>
       </c>
     </row>
     <row r="7">
@@ -666,16 +686,19 @@
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>46.26654434204102</v>
+        <v>59.86569213867188</v>
       </c>
       <c r="H7" t="n">
-        <v>62.70071792602539</v>
+        <v>57.69221115112305</v>
       </c>
       <c r="I7" t="n">
-        <v>54.81847381591797</v>
+        <v>1113.484985351562</v>
       </c>
       <c r="J7" t="n">
-        <v>29.7108154296875</v>
+        <v>48.93339157104492</v>
+      </c>
+      <c r="K7" t="n">
+        <v>17.96843338012695</v>
       </c>
     </row>
     <row r="8">
@@ -698,16 +721,19 @@
         <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>56.86635971069336</v>
+        <v>59.51290130615234</v>
       </c>
       <c r="H8" t="n">
-        <v>58.84476089477539</v>
+        <v>51.49053573608398</v>
       </c>
       <c r="I8" t="n">
-        <v>47.7228889465332</v>
+        <v>1051.355346679688</v>
       </c>
       <c r="J8" t="n">
-        <v>24.05666351318359</v>
+        <v>41.90756988525391</v>
+      </c>
+      <c r="K8" t="n">
+        <v>13.28983879089355</v>
       </c>
     </row>
     <row r="9">
@@ -730,16 +756,19 @@
         <v>18.6</v>
       </c>
       <c r="G9" t="n">
-        <v>59.51688385009766</v>
+        <v>53.95771408081055</v>
       </c>
       <c r="H9" t="n">
-        <v>67.26350402832031</v>
+        <v>60.65985870361328</v>
       </c>
       <c r="I9" t="n">
-        <v>50.96973419189453</v>
+        <v>1516.516967773438</v>
       </c>
       <c r="J9" t="n">
-        <v>22.27042198181152</v>
+        <v>42.76549530029297</v>
+      </c>
+      <c r="K9" t="n">
+        <v>13.46292114257812</v>
       </c>
     </row>
     <row r="10">
@@ -762,16 +791,19 @@
         <v>18.9</v>
       </c>
       <c r="G10" t="n">
-        <v>58.77445220947266</v>
+        <v>58.35604858398438</v>
       </c>
       <c r="H10" t="n">
-        <v>65.75988006591797</v>
+        <v>54.62445068359375</v>
       </c>
       <c r="I10" t="n">
-        <v>45.09534072875977</v>
+        <v>1073.451538085938</v>
       </c>
       <c r="J10" t="n">
-        <v>26.55727958679199</v>
+        <v>29.3164176940918</v>
+      </c>
+      <c r="K10" t="n">
+        <v>17.009033203125</v>
       </c>
     </row>
     <row r="11">
@@ -794,16 +826,19 @@
         <v>19.8</v>
       </c>
       <c r="G11" t="n">
-        <v>62.67424392700195</v>
+        <v>61.85854721069336</v>
       </c>
       <c r="H11" t="n">
-        <v>82.80182647705078</v>
+        <v>53.72707748413086</v>
       </c>
       <c r="I11" t="n">
-        <v>61.09664154052734</v>
+        <v>1229.29833984375</v>
       </c>
       <c r="J11" t="n">
-        <v>29.1312084197998</v>
+        <v>47.36355209350586</v>
+      </c>
+      <c r="K11" t="n">
+        <v>13.33101272583008</v>
       </c>
     </row>
     <row r="12">
@@ -826,16 +861,19 @@
         <v>24.2</v>
       </c>
       <c r="G12" t="n">
-        <v>49.40594863891602</v>
+        <v>55.42659378051758</v>
       </c>
       <c r="H12" t="n">
-        <v>61.46982574462891</v>
+        <v>67.99900817871094</v>
       </c>
       <c r="I12" t="n">
-        <v>68.72349548339844</v>
+        <v>1800.546630859375</v>
       </c>
       <c r="J12" t="n">
-        <v>27.90011405944824</v>
+        <v>38.83723068237305</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20.5457878112793</v>
       </c>
     </row>
     <row r="13">
@@ -858,16 +896,19 @@
         <v>30.8</v>
       </c>
       <c r="G13" t="n">
-        <v>35.6900520324707</v>
+        <v>39.48336791992188</v>
       </c>
       <c r="H13" t="n">
-        <v>56.4548454284668</v>
+        <v>31.50955200195312</v>
       </c>
       <c r="I13" t="n">
-        <v>43.76027679443359</v>
+        <v>1066.476684570312</v>
       </c>
       <c r="J13" t="n">
-        <v>41.85620498657227</v>
+        <v>44.34108734130859</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20.5489387512207</v>
       </c>
     </row>
   </sheetData>
